--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/findById-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/findById-bbt-form.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="62">
   <si>
     <t>Statement: WorkoutSessionRepository.findById(id) – retrieves session with exercises.</t>
   </si>
@@ -121,7 +121,10 @@
     <t>id = ""</t>
   </si>
   <si>
-    <t>id = "a"</t>
+    <t>id = "a" (inex)</t>
+  </si>
+  <si>
+    <t>id = "a" (exist)</t>
   </si>
   <si>
     <t>BVA</t>
@@ -130,7 +133,10 @@
     <t>BVA-1 Empty</t>
   </si>
   <si>
-    <t>BVA-2 OneChar</t>
+    <t>BVA-2 InexChar</t>
+  </si>
+  <si>
+    <t>BVA-3 ExistChar</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -152,6 +158,9 @@
   </si>
   <si>
     <t>BVA-2</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
   </si>
   <si>
     <t>Testing</t>
@@ -836,7 +845,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -877,6 +886,17 @@
         <v>34</v>
       </c>
     </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -885,7 +905,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -900,7 +920,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>20</v>
@@ -917,7 +937,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -934,7 +954,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>34</v>
@@ -943,6 +963,23 @@
         <v>29</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -954,7 +991,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -970,10 +1007,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>20</v>
@@ -996,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>26</v>
@@ -1016,7 +1053,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>29</v>
@@ -1033,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>33</v>
@@ -1053,7 +1090,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>34</v>
@@ -1062,6 +1099,26 @@
         <v>29</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1090,16 +1147,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1107,45 +1164,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1154,19 +1211,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/findById-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/findById-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="62">
-  <si>
-    <t>Statement: WorkoutSessionRepository.findById(id) – retrieves session with exercises.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="59">
+  <si>
+    <t>Statement: WorkoutSessionRepository.findById(id) – Retrieves a single workout session with its exercises by ID. Returns the matching WorkoutSessionWithExercises on success. Throws NotFoundError("Workout session not found") if no session exists with the given ID.</t>
   </si>
   <si>
     <t/>
@@ -37,19 +37,19 @@
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible</t>
+    <t>Database is accessible. A workout session with the given ID may or may not exist.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;WorkoutSessionWithExercises&gt; | throws NotFoundError</t>
+    <t>Output: Promise&lt;WorkoutSessionWithExercises&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Returns record or throws NotFoundError.</t>
+    <t>On success: WorkoutSessionWithExercises returned with result equal to MOCK_SESSION_WITH_EXERCISES, result.id: SESSION_ID, result.exercises.length: 1. On failure: NotFoundError("Workout session not found") thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -67,10 +67,10 @@
     <t>Session existence</t>
   </si>
   <si>
-    <t>Found</t>
-  </si>
-  <si>
-    <t>Not found (NotFoundError)</t>
+    <t>Existing ID → WorkoutSessionWithExercises returned with result equal to MOCK_SESSION_WITH_EXERCISES, result.id: SESSION_ID, result.exercises.length: 1</t>
+  </si>
+  <si>
+    <t>Non-existent ID → NotFoundError("Workout session not found")</t>
   </si>
   <si>
     <t>No TC</t>
@@ -91,10 +91,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>Existing ID</t>
-  </si>
-  <si>
-    <t>Returns session</t>
+    <t>id: SESSION_ID (session exists)</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned with result equal to MOCK_SESSION_WITH_EXERCISES, result.id: SESSION_ID, result.exercises.length: 1</t>
   </si>
   <si>
     <t>Passed</t>
@@ -103,10 +103,10 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>"nonexistent-id"</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
+    <t>id: NONEXISTENT_ID (no session with that ID)</t>
+  </si>
+  <si>
+    <t>throws NotFoundError("Workout session not found")</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -118,25 +118,31 @@
     <t>ID length</t>
   </si>
   <si>
-    <t>id = ""</t>
-  </si>
-  <si>
-    <t>id = "a" (inex)</t>
-  </si>
-  <si>
-    <t>id = "a" (exist)</t>
+    <t>0 chars (empty, not found), 1 char (not found), 1 char (found)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Empty</t>
-  </si>
-  <si>
-    <t>BVA-2 InexChar</t>
-  </si>
-  <si>
-    <t>BVA-3 ExistChar</t>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>id: "" (no session with that ID)</t>
+  </si>
+  <si>
+    <t>throws NotFoundError</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>id: "a" (no session with that ID)</t>
+  </si>
+  <si>
+    <t>id: "a" (session exists with id: "a")</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned with result.id: "a", result equal to { ...MOCK_SESSION_WITH_EXERCISES, id: "a" }</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -145,24 +151,9 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Existing session ID</t>
-  </si>
-  <si>
-    <t>Returns WorkoutSessionWithExercises</t>
-  </si>
-  <si>
-    <t>Non-existent ID</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>BVA-2</t>
-  </si>
-  <si>
-    <t>BVA-3</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -193,7 +184,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>WSM-05</t>
+    <t>REPO-20</t>
   </si>
   <si>
     <t>n/a</t>
@@ -759,7 +750,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -845,7 +836,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -873,28 +864,6 @@
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +889,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>20</v>
@@ -937,13 +906,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>26</v>
@@ -957,10 +926,10 @@
         <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>26</v>
@@ -971,13 +940,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>26</v>
@@ -1007,10 +976,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>20</v>
@@ -1033,10 +1002,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>26</v>
@@ -1053,7 +1022,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>29</v>
@@ -1070,13 +1039,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>26</v>
@@ -1090,13 +1059,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>26</v>
@@ -1110,13 +1079,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>26</v>
@@ -1147,16 +1116,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1164,39 +1133,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B3" s="1">
         <v>5</v>
@@ -1211,19 +1180,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
